--- a/tests/runs/run_20/evidence_ReportTypeB.xlsx
+++ b/tests/runs/run_20/evidence_ReportTypeB.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReportTypeB Evidence" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Trader Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,20 +28,37 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="0000335B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="002E7D32"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="00D9383A"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000335B"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +71,18 @@
         <bgColor rgb="0000335B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+        <bgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -64,26 +93,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,118 +486,440 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Report Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Report Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage Period</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Violation Marker</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Validation Status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Threshold1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Threshold2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Threshold3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Threshold4</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Breach Details</t>
+          <t>Xetra Monthly Trader Summary — 2026-06-01 to 2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20260618</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ReportTypeB</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+          <t>Report ID: XETRA-MA-202606  |  Venue: XETR  |  Member: FRAUAS01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TraderID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TraderName</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>TotalTrades</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>TotalVolume</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>AvgTradeSize</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>TopInstrument</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>MonthViol</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>ViolationCount</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>ViolationDetails</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>ComplianceRating</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>T-3011</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Fischer, Moritz</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2535386.43</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>7972.91</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>adidas AG (DE000A1EWWW0)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>No violation marker detected (MonthViol = 'N')</t>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>T-6091</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Krause, Sophie</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>5392401.68</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>29306.53</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>BASF SE (DE000BASF111)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>2x late trade booking, 3x position limit breach</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>T-5023</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Becker, Jan</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>3100319.81</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>13421.30</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Group (DE0007100000)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>T-4055</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Hoffmann, Lena</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>FX Spot</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>6742665.56</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>32891.05</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Münchener Rück (DE0008430026)</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>T-2087</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Schmidt, Anna</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Derivatives</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>9515286.57</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>45096.14</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Infineon Technologies (DE0006231004)</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Traders: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Trades: 1149</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Volume: EUR 27286060.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Violations Found: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Overall Status: Violation</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>